--- a/data/trans_dic/P11_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P11_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que el dolor le dificultó su trabajo habitual las últimas 4 semanas</t>
+          <t>Población a la que el dolor le dificultó su trabajo habitual las últimas 4 semanas (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,86; 18,72</t>
+          <t>12,13; 18,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,21; 15,8</t>
+          <t>9,07; 15,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,35; 18,31</t>
+          <t>11,41; 18,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,13; 24,73</t>
+          <t>18,05; 25,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,77; 27,32</t>
+          <t>17,84; 27,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,61; 21,01</t>
+          <t>12,38; 21,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,73; 22,09</t>
+          <t>13,82; 22,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,02; 31,14</t>
+          <t>24,05; 31,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,17; 20,49</t>
+          <t>15,15; 20,91</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,71; 17,35</t>
+          <t>11,49; 16,45</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,35; 18,94</t>
+          <t>13,15; 18,53</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,66; 26,76</t>
+          <t>21,64; 26,8</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,79; 15,6</t>
+          <t>8,62; 15,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,65; 20,47</t>
+          <t>12,59; 20,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,02; 16,09</t>
+          <t>9,19; 16,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,34; 26,75</t>
+          <t>19,55; 27,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,5; 22,3</t>
+          <t>14,34; 22,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,86; 23,95</t>
+          <t>14,74; 23,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,22; 23,69</t>
+          <t>15,48; 23,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>24,75; 32,66</t>
+          <t>24,9; 33,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,84; 18,24</t>
+          <t>12,71; 18,16</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,59; 20,71</t>
+          <t>14,51; 20,59</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13,14; 18,83</t>
+          <t>13,15; 18,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,84; 28,29</t>
+          <t>23,15; 28,58</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,15; 21,82</t>
+          <t>15,27; 21,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,86; 27,46</t>
+          <t>19,84; 27,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,72; 24,36</t>
+          <t>16,94; 23,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,76; 32,2</t>
+          <t>6,97; 32,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,47; 37,01</t>
+          <t>23,42; 37,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,22; 38,89</t>
+          <t>26,21; 38,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,43; 35,87</t>
+          <t>21,81; 36,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,77; 52,58</t>
+          <t>39,91; 52,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,99; 24,32</t>
+          <t>17,98; 24,25</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22,64; 28,84</t>
+          <t>22,51; 29,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19,25; 25,93</t>
+          <t>19,16; 25,74</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,32; 36,47</t>
+          <t>10,23; 36,13</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,45; 25,32</t>
+          <t>20,37; 25,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,77; 24,78</t>
+          <t>19,69; 24,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,25; 24,41</t>
+          <t>19,52; 24,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28,16; 33,85</t>
+          <t>28,01; 33,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,08; 29,5</t>
+          <t>23,08; 29,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,99; 28,71</t>
+          <t>21,64; 28,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,69; 27,81</t>
+          <t>21,64; 27,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,15; 73,43</t>
+          <t>34,04; 69,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,33; 26,06</t>
+          <t>22,29; 26,08</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,32; 25,46</t>
+          <t>21,36; 25,51</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,35; 25,26</t>
+          <t>21,22; 25,12</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31,9; 56,74</t>
+          <t>31,86; 58,91</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,52; 26,55</t>
+          <t>17,9; 26,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,43; 23,77</t>
+          <t>16,56; 23,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20,53; 27,39</t>
+          <t>20,27; 27,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28,74; 37,43</t>
+          <t>29,36; 37,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,02; 32,75</t>
+          <t>25,16; 32,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,2; 42,99</t>
+          <t>35,51; 42,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,01; 39,43</t>
+          <t>32,66; 39,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>30,78; 47,78</t>
+          <t>31,55; 47,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23,11; 29,04</t>
+          <t>23,12; 28,98</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28,83; 34,08</t>
+          <t>28,8; 34,09</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27,81; 32,75</t>
+          <t>27,84; 33,03</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>31,48; 42,24</t>
+          <t>31,3; 42,14</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,46; 10,2</t>
+          <t>4,36; 10,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,26; 11,63</t>
+          <t>4,56; 11,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,06; 8,59</t>
+          <t>3,08; 8,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,89; 19,31</t>
+          <t>5,97; 19,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33,08; 38,61</t>
+          <t>33,33; 38,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,94; 40,9</t>
+          <t>35,08; 40,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,72; 36,77</t>
+          <t>30,7; 36,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>37,48; 44,0</t>
+          <t>37,48; 43,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28,14; 32,75</t>
+          <t>28,22; 32,71</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29,41; 34,58</t>
+          <t>29,25; 34,43</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24,8; 30,09</t>
+          <t>25,22; 30,24</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>30,51; 36,57</t>
+          <t>30,46; 36,67</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,99; 19,74</t>
+          <t>16,95; 19,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,37; 20,31</t>
+          <t>17,61; 20,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,25; 19,96</t>
+          <t>17,23; 20,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19,22; 27,67</t>
+          <t>19,65; 27,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>27,73; 30,78</t>
+          <t>27,43; 30,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,65; 32,77</t>
+          <t>29,77; 32,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,08; 30,25</t>
+          <t>27,15; 30,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>36,23; 52,29</t>
+          <t>35,99; 51,82</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22,7; 24,88</t>
+          <t>22,76; 24,91</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24,04; 26,26</t>
+          <t>24,11; 26,22</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22,71; 24,88</t>
+          <t>22,71; 24,9</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>29,61; 39,19</t>
+          <t>29,84; 40,12</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que el dolor le dificultó su trabajo habitual las últimas 4 semanas</t>
+          <t>Población a la que el dolor le dificultó su trabajo habitual las últimas 4 semanas (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>56169; 88692</t>
+          <t>57485; 89343</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40017; 68621</t>
+          <t>39412; 67613</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48156; 77698</t>
+          <t>48434; 78335</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>91325; 124608</t>
+          <t>90925; 126274</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>54506; 83781</t>
+          <t>54699; 83974</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39643; 66071</t>
+          <t>38915; 66588</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47268; 76062</t>
+          <t>47564; 76593</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>107158; 138939</t>
+          <t>107293; 139240</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>118390; 159919</t>
+          <t>118250; 163226</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>87659; 129905</t>
+          <t>86017; 123192</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>102595; 145587</t>
+          <t>101035; 142400</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>205799; 254228</t>
+          <t>205610; 254548</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32268; 57229</t>
+          <t>31644; 56663</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52861; 85516</t>
+          <t>52589; 86627</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33937; 60534</t>
+          <t>34577; 60411</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>87301; 120755</t>
+          <t>88252; 122730</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>53936; 82919</t>
+          <t>53318; 82792</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50080; 80732</t>
+          <t>49695; 79499</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56370; 87726</t>
+          <t>57328; 88524</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>94530; 124765</t>
+          <t>95114; 126383</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>94895; 134736</t>
+          <t>93905; 134173</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>110109; 156357</t>
+          <t>109517; 155457</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>98077; 140607</t>
+          <t>98149; 137895</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>190338; 235813</t>
+          <t>192937; 238235</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>82178; 118359</t>
+          <t>82838; 117382</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>124179; 171680</t>
+          <t>124072; 169311</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>86660; 126238</t>
+          <t>87755; 124145</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51780; 214866</t>
+          <t>46503; 217068</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>37706; 62103</t>
+          <t>39297; 63102</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>67940; 100788</t>
+          <t>67922; 100519</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35141; 58814</t>
+          <t>35757; 60560</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>66384; 87758</t>
+          <t>66609; 87450</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>127786; 172690</t>
+          <t>127687; 172228</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>200276; 255046</t>
+          <t>199058; 257260</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>131322; 176856</t>
+          <t>130667; 175579</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>86125; 304228</t>
+          <t>85352; 301415</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>253245; 313496</t>
+          <t>252281; 314403</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>228329; 286192</t>
+          <t>227434; 283660</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>219735; 278681</t>
+          <t>222873; 279088</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>291384; 350237</t>
+          <t>289879; 351610</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>164845; 210686</t>
+          <t>164891; 213001</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>168392; 219784</t>
+          <t>165692; 215049</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>177863; 228049</t>
+          <t>177406; 227974</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>333972; 718239</t>
+          <t>332933; 675935</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>435980; 508813</t>
+          <t>435330; 509237</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>409465; 489101</t>
+          <t>410360; 490031</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>418843; 495475</t>
+          <t>416247; 492802</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>642086; 1142032</t>
+          <t>641389; 1185718</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>61412; 93056</t>
+          <t>62752; 93783</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>83353; 120566</t>
+          <t>83987; 119375</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>126769; 169088</t>
+          <t>125159; 167378</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>136518; 177807</t>
+          <t>139481; 180099</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>142329; 186277</t>
+          <t>143118; 186500</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>267705; 326943</t>
+          <t>270089; 324381</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>235363; 289979</t>
+          <t>240159; 292354</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>258826; 401799</t>
+          <t>265270; 399916</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>212436; 266931</t>
+          <t>212515; 266439</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>365541; 432070</t>
+          <t>365156; 432244</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>376189; 442963</t>
+          <t>376571; 446864</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>414259; 555801</t>
+          <t>411918; 554537</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13309; 30409</t>
+          <t>12988; 29957</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11302; 30829</t>
+          <t>12096; 29875</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8682; 24338</t>
+          <t>8739; 24838</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14167; 46432</t>
+          <t>14368; 47425</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>413067; 482107</t>
+          <t>416188; 484368</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>387627; 453724</t>
+          <t>389190; 454118</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>330297; 395302</t>
+          <t>330073; 394077</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>284771; 334328</t>
+          <t>284763; 332201</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>435294; 506592</t>
+          <t>436605; 506072</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>404224; 475281</t>
+          <t>401938; 473251</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>336946; 408847</t>
+          <t>342638; 410818</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>305192; 365826</t>
+          <t>304722; 366773</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>555562; 645566</t>
+          <t>554380; 638869</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>591475; 691674</t>
+          <t>599608; 696043</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>579636; 670721</t>
+          <t>579015; 673924</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>648153; 933385</t>
+          <t>662678; 936357</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>936804; 1039619</t>
+          <t>926587; 1041082</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1051414; 1161993</t>
+          <t>1055887; 1163511</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>950118; 1061366</t>
+          <t>952785; 1062509</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1294954; 1868919</t>
+          <t>1286358; 1851867</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1509474; 1653787</t>
+          <t>1513361; 1655783</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1671036; 1825052</t>
+          <t>1675644; 1822749</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1559901; 1709370</t>
+          <t>1560262; 1710589</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2056758; 2722785</t>
+          <t>2072808; 2787337</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P11_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P11_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,13; 18,86</t>
+          <t>12,06; 18,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,07; 15,57</t>
+          <t>9,4; 16,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,41; 18,46</t>
+          <t>10,77; 18,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,05; 25,06</t>
+          <t>17,98; 24,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,84; 27,38</t>
+          <t>17,9; 27,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,38; 21,18</t>
+          <t>12,41; 21,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,82; 22,25</t>
+          <t>13,86; 22,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,05; 31,21</t>
+          <t>24,33; 30,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,15; 20,91</t>
+          <t>15,42; 20,76</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,49; 16,45</t>
+          <t>11,37; 16,77</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,15; 18,53</t>
+          <t>13,19; 18,97</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,64; 26,8</t>
+          <t>21,88; 26,75</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,36%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,62; 15,44</t>
+          <t>8,77; 15,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,59; 20,73</t>
+          <t>12,26; 20,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,19; 16,06</t>
+          <t>9,05; 16,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,55; 27,18</t>
+          <t>18,75; 26,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,34; 22,26</t>
+          <t>14,34; 22,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,74; 23,58</t>
+          <t>14,46; 23,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,48; 23,9</t>
+          <t>15,48; 23,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>24,9; 33,08</t>
+          <t>25,46; 32,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,71; 18,16</t>
+          <t>12,53; 17,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,51; 20,59</t>
+          <t>14,21; 20,51</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13,15; 18,47</t>
+          <t>13,07; 18,4</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,15; 28,58</t>
+          <t>22,76; 28,13</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>34,06%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,27; 21,64</t>
+          <t>15,43; 21,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,84; 27,08</t>
+          <t>19,84; 27,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,94; 23,96</t>
+          <t>16,99; 24,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,97; 32,53</t>
+          <t>25,86; 34,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,42; 37,61</t>
+          <t>22,65; 36,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,21; 38,79</t>
+          <t>26,56; 38,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,81; 36,94</t>
+          <t>21,61; 36,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,91; 52,39</t>
+          <t>38,81; 50,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,98; 24,25</t>
+          <t>18,18; 24,07</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22,51; 29,09</t>
+          <t>22,67; 28,86</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19,16; 25,74</t>
+          <t>18,79; 25,67</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,23; 36,13</t>
+          <t>30,69; 37,78</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>32,39%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,37; 25,39</t>
+          <t>20,52; 25,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,69; 24,56</t>
+          <t>19,72; 24,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,52; 24,45</t>
+          <t>19,55; 24,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28,01; 33,98</t>
+          <t>27,72; 33,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,08; 29,82</t>
+          <t>23,37; 29,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,64; 28,09</t>
+          <t>21,71; 27,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,64; 27,8</t>
+          <t>21,6; 27,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,04; 69,11</t>
+          <t>32,02; 37,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,29; 26,08</t>
+          <t>22,35; 26,28</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,36; 25,51</t>
+          <t>21,44; 25,29</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,22; 25,12</t>
+          <t>21,28; 25,18</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31,86; 58,91</t>
+          <t>30,49; 34,5</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>40,14%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,9; 26,75</t>
+          <t>18,07; 27,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,56; 23,54</t>
+          <t>16,43; 23,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20,27; 27,11</t>
+          <t>20,72; 27,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29,36; 37,91</t>
+          <t>28,14; 36,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,16; 32,79</t>
+          <t>25,09; 32,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,51; 42,65</t>
+          <t>35,67; 42,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,66; 39,76</t>
+          <t>32,45; 39,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>31,55; 47,56</t>
+          <t>43,3; 48,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23,12; 28,98</t>
+          <t>23,12; 29,25</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28,8; 34,09</t>
+          <t>28,77; 33,9</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27,84; 33,03</t>
+          <t>27,8; 32,79</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>31,3; 42,14</t>
+          <t>37,68; 42,49</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,4%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,36; 10,05</t>
+          <t>4,24; 10,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,56; 11,27</t>
+          <t>4,53; 11,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,08; 8,77</t>
+          <t>3,03; 9,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,97; 19,72</t>
+          <t>6,1; 18,51</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33,33; 38,79</t>
+          <t>33,47; 38,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35,08; 40,94</t>
+          <t>35,11; 41,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,7; 36,65</t>
+          <t>30,45; 36,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>37,48; 43,72</t>
+          <t>36,63; 42,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28,22; 32,71</t>
+          <t>28,13; 32,57</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29,25; 34,43</t>
+          <t>29,55; 34,69</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25,22; 30,24</t>
+          <t>25,24; 30,17</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>30,46; 36,67</t>
+          <t>30,65; 36,26</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,13%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,95; 19,54</t>
+          <t>16,89; 19,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,61; 20,44</t>
+          <t>17,56; 20,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,23; 20,05</t>
+          <t>17,15; 20,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19,65; 27,76</t>
+          <t>25,14; 28,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>27,43; 30,82</t>
+          <t>27,71; 30,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,77; 32,81</t>
+          <t>29,66; 32,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,15; 30,28</t>
+          <t>27,11; 30,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>35,99; 51,82</t>
+          <t>35,99; 38,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22,76; 24,91</t>
+          <t>22,76; 24,77</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24,11; 26,22</t>
+          <t>24,19; 26,33</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22,71; 24,9</t>
+          <t>22,67; 24,81</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>29,84; 40,12</t>
+          <t>31,04; 33,1</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>106847</t>
+          <t>117577</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>122427</t>
+          <t>132887</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>229274</t>
+          <t>250464</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>57485; 89343</t>
+          <t>57120; 88582</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>39412; 67613</t>
+          <t>40821; 69748</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48434; 78335</t>
+          <t>45691; 76480</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>90925; 126274</t>
+          <t>98716; 136913</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>54699; 83974</t>
+          <t>54910; 84343</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>38915; 66588</t>
+          <t>39026; 67268</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47564; 76593</t>
+          <t>47719; 77087</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>107293; 139240</t>
+          <t>118439; 149536</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>118250; 163226</t>
+          <t>120362; 162051</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>86017; 123192</t>
+          <t>85118; 125551</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>101035; 142400</t>
+          <t>101389; 145789</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>205610; 254548</t>
+          <t>226693; 277075</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>104162</t>
+          <t>107185</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>109674</t>
+          <t>122220</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>213835</t>
+          <t>229406</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31644; 56663</t>
+          <t>32183; 57480</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52589; 86627</t>
+          <t>51226; 84908</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34577; 60411</t>
+          <t>34052; 60190</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88252; 122730</t>
+          <t>90430; 127093</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>53318; 82792</t>
+          <t>53343; 85202</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49695; 79499</t>
+          <t>48729; 79981</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57328; 88524</t>
+          <t>57319; 88614</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>95114; 126383</t>
+          <t>107545; 136861</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93905; 134173</t>
+          <t>92552; 130140</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>109517; 155457</t>
+          <t>107246; 154792</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>98149; 137895</t>
+          <t>97544; 137395</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>192937; 238235</t>
+          <t>205910; 254479</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>131308</t>
+          <t>140215</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>76654</t>
+          <t>83936</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>207962</t>
+          <t>224151</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>82838; 117382</t>
+          <t>83688; 119034</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>124072; 169311</t>
+          <t>124070; 171528</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>87755; 124145</t>
+          <t>88044; 125747</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46503; 217068</t>
+          <t>121683; 163070</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>39297; 63102</t>
+          <t>37998; 62057</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>67922; 100519</t>
+          <t>68837; 99124</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35757; 60560</t>
+          <t>35423; 60209</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>66609; 87450</t>
+          <t>72761; 94866</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>127687; 172228</t>
+          <t>129112; 170959</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>199058; 257260</t>
+          <t>200546; 255223</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>130667; 175579</t>
+          <t>128188; 175092</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>85352; 301415</t>
+          <t>201951; 248596</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>319246</t>
+          <t>346116</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>476451</t>
+          <t>299358</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>795697</t>
+          <t>645475</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>252281; 314403</t>
+          <t>254089; 311049</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>227434; 283660</t>
+          <t>227820; 286364</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>222873; 279088</t>
+          <t>223169; 280526</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>289879; 351610</t>
+          <t>313766; 376687</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>164891; 213001</t>
+          <t>166916; 212734</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>165692; 215049</t>
+          <t>166227; 213683</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>177406; 227974</t>
+          <t>177101; 225092</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>332933; 675935</t>
+          <t>275771; 322263</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>435330; 509237</t>
+          <t>436329; 513077</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>410360; 490031</t>
+          <t>411870; 485750</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>416247; 492802</t>
+          <t>417298; 493952</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>641389; 1185718</t>
+          <t>607697; 687530</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>157695</t>
+          <t>179921</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>351811</t>
+          <t>381372</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>509505</t>
+          <t>561293</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>62752; 93783</t>
+          <t>63338; 95471</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>83987; 119375</t>
+          <t>83334; 118771</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>125159; 167378</t>
+          <t>127929; 169245</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>139481; 180099</t>
+          <t>159810; 204819</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>143118; 186500</t>
+          <t>142691; 186130</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>270089; 324381</t>
+          <t>271262; 325759</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>240159; 292354</t>
+          <t>238637; 289958</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>265270; 399916</t>
+          <t>359584; 405838</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>212515; 266439</t>
+          <t>212517; 268907</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>365156; 432244</t>
+          <t>364799; 429788</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>376571; 446864</t>
+          <t>376003; 443580</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>411918; 554537</t>
+          <t>526942; 594130</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25914</t>
+          <t>25735</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>308612</t>
+          <t>334896</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>334526</t>
+          <t>360632</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12988; 29957</t>
+          <t>12654; 31396</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12096; 29875</t>
+          <t>12003; 29254</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8739; 24838</t>
+          <t>8584; 25667</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14368; 47425</t>
+          <t>14474; 43903</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>416188; 484368</t>
+          <t>417978; 481407</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>389190; 454118</t>
+          <t>389502; 458857</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>330073; 394077</t>
+          <t>327367; 393426</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>284763; 332201</t>
+          <t>308654; 359540</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>436605; 506072</t>
+          <t>435139; 503845</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>401938; 473251</t>
+          <t>406074; 476710</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>342638; 410818</t>
+          <t>342845; 409822</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>304722; 366773</t>
+          <t>330928; 391567</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>845172</t>
+          <t>916750</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1445629</t>
+          <t>1354670</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2290801</t>
+          <t>2271419</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>554380; 638869</t>
+          <t>552396; 639100</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>599608; 696043</t>
+          <t>597731; 693298</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>579015; 673924</t>
+          <t>576317; 672587</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>662678; 936357</t>
+          <t>864402; 971319</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>926587; 1041082</t>
+          <t>935909; 1041952</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1055887; 1163511</t>
+          <t>1051975; 1163360</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>952785; 1062509</t>
+          <t>951334; 1063959</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1286358; 1851867</t>
+          <t>1306938; 1402808</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1513361; 1655783</t>
+          <t>1513415; 1646858</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1675644; 1822749</t>
+          <t>1681743; 1830513</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1560262; 1710589</t>
+          <t>1557736; 1704478</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2072808; 2787337</t>
+          <t>2194777; 2340387</t>
         </is>
       </c>
     </row>
